--- a/frontend/public/forms/templates/par-template.xlsx
+++ b/frontend/public/forms/templates/par-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GIO\Desktop\CHERIE\CAPSTONE\frontend\public\forms\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642E11E8-E97B-42FF-858D-64DA6377272B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3813EF-3CA6-4EB7-9C86-424731508626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAR" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,26 +121,43 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -441,16 +458,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -458,73 +472,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -532,121 +488,186 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -939,10 +960,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I1" s="71" t="s">
+      <c r="I1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="71"/>
+      <c r="J1" s="10"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
@@ -950,622 +971,762 @@
       <c r="K2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
     </row>
     <row r="4" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
     </row>
     <row r="7" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="25"/>
-      <c r="H7" s="32" t="s">
+      <c r="B7" s="16"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="31"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-    </row>
-    <row r="8" spans="1:11" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:11" s="6" customFormat="1" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="38" t="s">
+      <c r="I7" s="77"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+    </row>
+    <row r="9" spans="1:11" s="5" customFormat="1" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="57" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="63" t="s">
+      <c r="E9" s="20"/>
+      <c r="F9" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="64"/>
-      <c r="H9" s="43" t="s">
+      <c r="G9" s="22"/>
+      <c r="H9" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:11" s="6" customFormat="1" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="39"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="60"/>
+      <c r="J9" s="20"/>
+    </row>
+    <row r="10" spans="1:11" s="5" customFormat="1" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="29"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="56"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="31"/>
       <c r="H11" s="29"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="56"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="31"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="30"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="41"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="34"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="30"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="41"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="34"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="41"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="34"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="30"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="41"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="34"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="30"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="41"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="30"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="41"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="34"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="30"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="41"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="34"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="30"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="41"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="34"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="30"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="41"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="34"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="30"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="41"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="34"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="30"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="41"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="34"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="30"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="41"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="34"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="30"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="41"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="34"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="30"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="41"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="34"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="30"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="41"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="34"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="30"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="41"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="34"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="30"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="41"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="34"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="30"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="41"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="34"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="30"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="41"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="34"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="30"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="41"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="34"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="30"/>
-      <c r="B32" s="40"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="41"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="34"/>
     </row>
     <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="30"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="41"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="34"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="30"/>
-      <c r="B34" s="40"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="41"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="34"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="30"/>
-      <c r="B35" s="40"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="41"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="34"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="30"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="41"/>
+      <c r="A36" s="32"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="34"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="30"/>
-      <c r="B37" s="40"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="41"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="34"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="30"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="41"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="34"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="30"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="40"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="41"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="34"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="30"/>
-      <c r="B40" s="40"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="40" t="s">
+      <c r="A40" s="32"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="73"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="76"/>
-      <c r="J40" s="77"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="39"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="74" t="s">
+      <c r="A41" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B41" s="40"/>
-      <c r="C41" s="73"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="73"/>
-      <c r="I41" s="73"/>
-      <c r="J41" s="41"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
+      <c r="J41" s="34"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="75"/>
-      <c r="B42" s="53"/>
-      <c r="C42" s="72"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="72"/>
-      <c r="J42" s="54"/>
+      <c r="A42" s="79"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="42"/>
     </row>
     <row r="43" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="69" t="s">
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="70"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="7"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="47"/>
+      <c r="K43" s="6"/>
     </row>
     <row r="44" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="34"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="7"/>
+      <c r="A44" s="48"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="50"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="6"/>
     </row>
     <row r="45" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="20"/>
-      <c r="B45" s="61"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="61"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="61"/>
-      <c r="H45" s="61"/>
-      <c r="I45" s="61"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="7"/>
-    </row>
-    <row r="46" spans="1:11" s="6" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="17"/>
-      <c r="B46" s="62" t="s">
+      <c r="A45" s="55"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="58"/>
+      <c r="K45" s="6"/>
+    </row>
+    <row r="46" spans="1:11" s="5" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="59"/>
+      <c r="B46" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="62"/>
-      <c r="D46" s="62"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="47" t="s">
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="49"/>
-      <c r="K46" s="5"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="63"/>
+      <c r="J46" s="64"/>
+      <c r="K46" s="4"/>
     </row>
     <row r="47" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
-      <c r="B47" s="61"/>
-      <c r="C47" s="61"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="61"/>
-      <c r="I47" s="61"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="7"/>
-    </row>
-    <row r="48" spans="1:11" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="17"/>
-      <c r="B48" s="51" t="s">
+      <c r="A47" s="55"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="56"/>
+      <c r="J47" s="58"/>
+      <c r="K47" s="6"/>
+    </row>
+    <row r="48" spans="1:11" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="59"/>
+      <c r="B48" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="51"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="50" t="s">
+      <c r="C48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="G48" s="51"/>
-      <c r="H48" s="51"/>
-      <c r="I48" s="51"/>
-      <c r="J48" s="52"/>
-      <c r="K48" s="5"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="68"/>
+      <c r="K48" s="4"/>
     </row>
     <row r="49" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="20"/>
-      <c r="B49" s="61"/>
-      <c r="C49" s="61"/>
-      <c r="D49" s="61"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61"/>
-      <c r="J49" s="22"/>
-      <c r="K49" s="7"/>
-    </row>
-    <row r="50" spans="1:11" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="15"/>
-      <c r="B50" s="45" t="s">
+      <c r="A49" s="55"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="58"/>
+      <c r="K49" s="6"/>
+    </row>
+    <row r="50" spans="1:11" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="69"/>
+      <c r="B50" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="44" t="s">
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="5"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="73"/>
+      <c r="K50" s="4"/>
     </row>
     <row r="51" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="10"/>
+      <c r="A52" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="148">
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B9:C10"/>
+    <mergeCell ref="F50:J50"/>
+    <mergeCell ref="F46:J46"/>
+    <mergeCell ref="F48:J48"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F27:G27"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="B42:J42"/>
     <mergeCell ref="B41:J41"/>
@@ -1590,130 +1751,6 @@
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B9:C10"/>
-    <mergeCell ref="F50:J50"/>
-    <mergeCell ref="F46:J46"/>
-    <mergeCell ref="F48:J48"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="1.25" right="1" top="1" bottom="0.5" header="0" footer="0.5"/>
